--- a/Dataset/3_label/OPENING_OPENING_V2_0.8 divisions_per_second.xlsx
+++ b/Dataset/3_label/OPENING_OPENING_V2_0.8 divisions_per_second.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D195"/>
+  <dimension ref="A1:D201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3942,6 +3942,114 @@
         </is>
       </c>
     </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>OPENING_OPENING_V2_0.8 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>40600</v>
+      </c>
+      <c r="C196" t="n">
+        <v>70</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>OPENING_OPENING_V2_0.8 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>40800</v>
+      </c>
+      <c r="C197" t="n">
+        <v>70</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>OPENING_OPENING_V2_0.8 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>41000</v>
+      </c>
+      <c r="C198" t="n">
+        <v>70</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>OPENING_OPENING_V2_0.8 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>41200</v>
+      </c>
+      <c r="C199" t="n">
+        <v>70</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>OPENING_OPENING_V2_0.8 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>41400</v>
+      </c>
+      <c r="C200" t="n">
+        <v>70</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>OPENING_OPENING_V2_0.8 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>41600</v>
+      </c>
+      <c r="C201" t="n">
+        <v>70</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
